--- a/docs/papers/insumos_master.xlsx.xlsx
+++ b/docs/papers/insumos_master.xlsx.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd1e85c08a3c974c/Desktop/TFM/TFM_Model/docs/papers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F25DC773A252ABDACC104872211F6A4E5ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FD9F3F1-F7C2-4805-AF45-F528C0CF1F86}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC104872211F6A4E5ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD5C2FAA-8F15-4BF7-82A1-75948B3C2A8F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="1" r:id="rId1"/>
     <sheet name="Papers" sheetId="2" r:id="rId2"/>
     <sheet name="Datasets" sheetId="3" r:id="rId3"/>
-    <sheet name="Plan_recomendado" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
+    <sheet name="Plan_recomendado" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="212">
   <si>
     <t>Campo</t>
   </si>
@@ -426,27 +427,6 @@
     <t>NewsCom-TOX</t>
   </si>
   <si>
-    <t>Corpus manual de toxicidad</t>
-  </si>
-  <si>
-    <t>4,359 comentarios</t>
-  </si>
-  <si>
-    <t>Toxicidad y nivel de toxicidad</t>
-  </si>
-  <si>
-    <t>CC BY-SA 4.0; disponible para investigación bajo solicitud</t>
-  </si>
-  <si>
-    <t>Validación externa fuerte; también apoyo de entrenamiento si logran acceso</t>
-  </si>
-  <si>
-    <t>Muy cercano al dominio de comentarios reales</t>
-  </si>
-  <si>
-    <t>No es descarga instantánea</t>
-  </si>
-  <si>
     <t>DETESTS-Dis</t>
   </si>
   <si>
@@ -655,6 +635,39 @@
   </si>
   <si>
     <t>Material fuerte para discusión y trabajo futuro</t>
+  </si>
+  <si>
+    <t>/corpus para detección de toxicidad Español Comentarios en respuesta a noticias sobre inmigración Repositorio público con carpeta data; tamaño no consolidado en la ficha consultada Tarea de detección de toxicidad y tarea de nivel de toxicidad Repositorio público en GitHub; sin solicitud adicional Validación externa principal Alta Disponible de inmediato, centrado en comentarios en español y alineado con toxicidad No es YouTube y su dominio temático está concentrado en noticias sobre inmigración https://github.com/alvaro-mazcu-herreros/DETOXIS_2021</t>
+  </si>
+  <si>
+    <t>DETOXIS</t>
+  </si>
+  <si>
+    <t>Dataset/corpus para detección de toxicidad</t>
+  </si>
+  <si>
+    <t>Comentarios en respuesta a noticias sobre inmigración</t>
+  </si>
+  <si>
+    <t>Repositorio público con carpeta data; tamaño no consolidado en la ficha consultada</t>
+  </si>
+  <si>
+    <t>Detección de toxicidad y nivel de toxicidad</t>
+  </si>
+  <si>
+    <t>Repositorio público en GitHub; sin solicitud adicional</t>
+  </si>
+  <si>
+    <t>Validación externa principal</t>
+  </si>
+  <si>
+    <t>Disponible de inmediato, centrado en comentarios en español y alineado con toxicidad</t>
+  </si>
+  <si>
+    <t>No es YouTube y su dominio temático está concentrado en noticias sobre inmigración</t>
+  </si>
+  <si>
+    <t>https://github.com/alvaro-mazcu-herreros/DETOXIS_2021?utm_source=chatgpt.com</t>
   </si>
 </sst>
 </file>
@@ -1403,11 +1416,11 @@
     <col min="1" max="1" width="48.9296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="64.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.1328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.06640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="61.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.3984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.9296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="53.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="59" bestFit="1" customWidth="1"/>
@@ -1530,75 +1543,75 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>202</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>204</v>
       </c>
       <c r="E4" t="s">
-        <v>132</v>
+        <v>205</v>
       </c>
       <c r="F4" t="s">
-        <v>133</v>
+        <v>206</v>
       </c>
       <c r="G4" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="H4" t="s">
-        <v>135</v>
+        <v>208</v>
       </c>
       <c r="I4" t="s">
         <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="K4" t="s">
-        <v>137</v>
+        <v>210</v>
       </c>
       <c r="L4" t="s">
-        <v>89</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C5" t="s">
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G5" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="H5" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="I5" t="s">
         <v>71</v>
       </c>
       <c r="J5" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="K5" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="L5" t="s">
         <v>98</v>
@@ -1606,10 +1619,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -1618,36 +1631,36 @@
         <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G6" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="H6" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I6" t="s">
         <v>71</v>
       </c>
       <c r="J6" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="K6" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="L6" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
@@ -1656,36 +1669,36 @@
         <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F7" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G7" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="H7" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="I7" t="s">
         <v>71</v>
       </c>
       <c r="J7" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="K7" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="L7" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B8" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
@@ -1694,66 +1707,66 @@
         <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="F8" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="G8" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H8" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I8" t="s">
         <v>71</v>
       </c>
       <c r="J8" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="K8" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="L8" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C9" t="s">
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E9" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F9" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G9" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="H9" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
       </c>
       <c r="J9" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="K9" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="L9" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -1762,6 +1775,24 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C4F57F6-9C29-467B-9D77-0EC012A52B40}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="255.59765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07DB6688-4EEC-43C1-99FC-38A975569FD9}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1774,100 +1805,100 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B3" t="s">
         <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B4" t="s">
         <v>130</v>
       </c>
       <c r="C4" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D4" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D5" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D6" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B7" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C7" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D7" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/docs/papers/insumos_master.xlsx.xlsx
+++ b/docs/papers/insumos_master.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd1e85c08a3c974c/Desktop/TFM/TFM_Model/docs/papers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC104872211F6A4E5ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD5C2FAA-8F15-4BF7-82A1-75948B3C2A8F}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_F25DC773A252ABDACC104872211F6A4E5ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C121271C-9034-44C3-AB72-ABF8859148B3}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,7 @@
     <sheet name="Readme" sheetId="1" r:id="rId1"/>
     <sheet name="Papers" sheetId="2" r:id="rId2"/>
     <sheet name="Datasets" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
-    <sheet name="Plan_recomendado" sheetId="4" r:id="rId5"/>
+    <sheet name="Plan_recomendado" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="211">
   <si>
     <t>Campo</t>
   </si>
@@ -635,9 +634,6 @@
   </si>
   <si>
     <t>Material fuerte para discusión y trabajo futuro</t>
-  </si>
-  <si>
-    <t>/corpus para detección de toxicidad Español Comentarios en respuesta a noticias sobre inmigración Repositorio público con carpeta data; tamaño no consolidado en la ficha consultada Tarea de detección de toxicidad y tarea de nivel de toxicidad Repositorio público en GitHub; sin solicitud adicional Validación externa principal Alta Disponible de inmediato, centrado en comentarios en español y alineado con toxicidad No es YouTube y su dominio temático está concentrado en noticias sobre inmigración https://github.com/alvaro-mazcu-herreros/DETOXIS_2021</t>
   </si>
   <si>
     <t>DETOXIS</t>
@@ -1543,40 +1539,40 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" t="s">
         <v>202</v>
-      </c>
-      <c r="B4" t="s">
-        <v>203</v>
       </c>
       <c r="C4" t="s">
         <v>30</v>
       </c>
       <c r="D4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E4" t="s">
         <v>204</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>205</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>206</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>207</v>
-      </c>
-      <c r="H4" t="s">
-        <v>208</v>
       </c>
       <c r="I4" t="s">
         <v>36</v>
       </c>
       <c r="J4" t="s">
+        <v>208</v>
+      </c>
+      <c r="K4" t="s">
         <v>209</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>210</v>
-      </c>
-      <c r="L4" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
@@ -1775,24 +1771,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C4F57F6-9C29-467B-9D77-0EC012A52B40}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="255.59765625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07DB6688-4EEC-43C1-99FC-38A975569FD9}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
